--- a/reference/agentic_engineering_layers.xlsx
+++ b/reference/agentic_engineering_layers.xlsx
@@ -577,7 +577,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>backend/agents/llm.py</t>
+          <t>backend/agents/llm/client.py</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>backend/agents/contracts.py, guardrails.py, resilience.py, access_control.py</t>
+          <t>backend/agents/llm/contracts.py, safety/guardrails.py, safety/resilience.py, safety/access_control.py</t>
         </is>
       </c>
     </row>
@@ -746,7 +746,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>agents/llm.py :: classify_severity, classify_team</t>
+          <t>agents/llm/client.py :: classify_severity, classify_team</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>agents/llm.py :: classify_severity_security vs. classify_severity</t>
+          <t>agents/llm/client.py :: classify_severity_security vs. classify_severity</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -790,7 +790,7 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>agents/llm.py :: _format_similar_ticket, format_runbook_doc</t>
+          <t>agents/llm/client.py :: _format_similar_ticket, format_runbook_doc</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>agents/contracts.py :: TriageResult.reasoning, RoutingResult.reasoning</t>
+          <t>agents/llm/contracts.py :: TriageResult.reasoning, RoutingResult.reasoning</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>agents/llm.py :: classify_severity_fast</t>
+          <t>agents/llm/client.py :: classify_severity_fast</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>agents/contracts.py :: TriageResult, RoutingResult</t>
+          <t>agents/llm/contracts.py :: TriageResult, RoutingResult</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>agents/contracts.py retry-then-escalate</t>
+          <t>agents/llm/contracts.py retry-then-escalate</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
